--- a/02_processed_data/entities_by_organization_type_2020_miyagi_processed.xlsx
+++ b/02_processed_data/entities_by_organization_type_2020_miyagi_processed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\miyagi-agricultural-recovery\miyagi-agricultural-recovery\02_processed_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1178054-6944-4C0A-9509-E6E1A22EA595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2015A14-FE66-4489-BC00-52DCE99B1710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E7FE4121-0E43-4645-A098-8C3236ACDFE0}"/>
   </bookViews>
@@ -1610,7 +1610,8 @@
     <col min="4" max="4" width="16.453125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20" style="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="11" width="10.36328125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" style="7" customWidth="1"/>
+    <col min="8" max="11" width="10.36328125" style="7" customWidth="1"/>
     <col min="12" max="12" width="15.1796875" style="7" customWidth="1"/>
     <col min="13" max="17" width="10.36328125" style="7" customWidth="1"/>
     <col min="18" max="18" width="31.7265625" style="7" bestFit="1" customWidth="1"/>
